--- a/test-data/Templates/SHS/M4 - Create Material type HAWA (DRINKS FG).xlsx
+++ b/test-data/Templates/SHS/M4 - Create Material type HAWA (DRINKS FG).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C281757E-B341-0C42-8446-821167BC09ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2285727B-5420-FC42-9ED9-1F72EE8485F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="15140" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -1332,7 +1332,7 @@
       <c r="B2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="1" t="s">

--- a/test-data/Templates/SHS/M4 - Create Material type HAWA (DRINKS FG).xlsx
+++ b/test-data/Templates/SHS/M4 - Create Material type HAWA (DRINKS FG).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2285727B-5420-FC42-9ED9-1F72EE8485F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE11EB6-00F4-1741-AACD-EF8FC0725421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="199">
   <si>
     <t>Object</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Request Number</t>
-  </si>
-  <si>
-    <t>Save</t>
   </si>
   <si>
     <t>Material</t>
@@ -1107,19 +1104,19 @@
     </row>
     <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -1142,7 +1139,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1155,10 +1152,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -1169,10 +1166,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1183,10 +1180,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -1197,10 +1194,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -1211,10 +1208,10 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
@@ -1225,10 +1222,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -1239,10 +1236,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.2">
@@ -1259,8 +1256,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{867B6D3F-F6EA-6D45-89A3-70B9CE3A4229}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D12" xr:uid="{58227CB0-C6D9-A247-A15C-D0FCE8718EAF}">
-      <formula1>"Save,Skip,Approve,Reject -&gt; Approve"</formula1>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D12" xr:uid="{86AF3705-A901-B444-93D3-4F7FF2BC528E}">
+      <formula1>"Save,Skip,Approve,Skip -&gt; Save,Skip -&gt; Approve,Reject -&gt; Approve"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1313,16 +1310,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -1330,55 +1327,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -1386,16 +1383,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -1407,13 +1404,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="O3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" t="s">
         <v>158</v>
-      </c>
-      <c r="O3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -1421,16 +1418,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -1438,13 +1435,13 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -1460,16 +1457,16 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -1477,13 +1474,13 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
@@ -1501,16 +1498,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1518,19 +1515,19 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -1564,16 +1561,16 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -1581,49 +1578,49 @@
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="J23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -1736,16 +1733,16 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -1753,25 +1750,25 @@
         <v>17</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="H33" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -1779,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -1787,21 +1784,21 @@
         <v>2</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
@@ -1809,25 +1806,25 @@
         <v>17</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="H38" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
@@ -1861,16 +1858,16 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
@@ -1878,28 +1875,28 @@
         <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
@@ -1914,16 +1911,16 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -1931,22 +1928,22 @@
         <v>17</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -1963,16 +1960,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
@@ -1980,19 +1977,19 @@
         <v>17</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="G54" s="2"/>
     </row>
@@ -2048,16 +2045,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
@@ -2065,31 +2062,31 @@
         <v>17</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G61" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="I61" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="J61" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -2099,16 +2096,16 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:40" x14ac:dyDescent="0.2">
@@ -2116,58 +2113,58 @@
         <v>17</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="M65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q65" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P65" s="1" t="s">
+      <c r="R65" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="S65" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:40" x14ac:dyDescent="0.2">
@@ -2181,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:40" x14ac:dyDescent="0.2">
@@ -2195,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:40" x14ac:dyDescent="0.2">
@@ -2203,16 +2200,16 @@
     </row>
     <row r="69" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:40" x14ac:dyDescent="0.2">
@@ -2220,22 +2217,22 @@
         <v>17</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:40" x14ac:dyDescent="0.2">
@@ -2245,16 +2242,16 @@
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.2">
@@ -2262,37 +2259,37 @@
         <v>17</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:40" x14ac:dyDescent="0.2">
@@ -2307,16 +2304,16 @@
     </row>
     <row r="78" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:40" x14ac:dyDescent="0.2">
@@ -2324,82 +2321,82 @@
         <v>17</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="I79" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="J79" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J79" s="2" t="s">
+      <c r="K79" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="L79" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="N79" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N79" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O79" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P79" s="2" t="s">
+      <c r="Q79" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Q79" s="2" t="s">
+      <c r="R79" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="R79" s="2" t="s">
+      <c r="S79" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="S79" s="2" t="s">
+      <c r="T79" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T79" s="2" t="s">
+      <c r="U79" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="U79" s="2" t="s">
+      <c r="V79" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V79" s="2" t="s">
+      <c r="W79" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="W79" s="2" t="s">
+      <c r="X79" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="X79" s="2" t="s">
+      <c r="Y79" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="Y79" s="2" t="s">
+      <c r="Z79" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Z79" s="2" t="s">
+      <c r="AA79" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="AA79" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="AB79" s="2"/>
       <c r="AC79" s="2"/>
@@ -2453,16 +2450,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -2470,55 +2467,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -2530,16 +2527,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -2547,49 +2544,49 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -2639,16 +2636,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -2656,13 +2653,13 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -2678,16 +2675,16 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -2695,37 +2692,37 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -2767,16 +2764,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -2784,55 +2781,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -2844,16 +2841,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -2861,13 +2858,13 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -2885,16 +2882,16 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -2902,22 +2899,22 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -2932,16 +2929,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -2949,31 +2946,31 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="I16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
@@ -3021,16 +3018,16 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
@@ -3038,55 +3035,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
@@ -3098,16 +3095,16 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
@@ -3115,16 +3112,16 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -3149,16 +3146,16 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>153</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -3202,25 +3199,25 @@
         <v>17</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -3437,16 +3434,16 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -3454,37 +3451,37 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -3499,16 +3496,16 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -3516,34 +3513,34 @@
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -3591,16 +3588,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -3608,55 +3605,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -3668,16 +3665,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -3685,28 +3682,28 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -3721,16 +3718,16 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -3738,37 +3735,37 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -3783,16 +3780,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -3800,34 +3797,34 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.2">
@@ -3837,16 +3834,16 @@
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.2">
@@ -3854,31 +3851,31 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="I20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.2">
@@ -3893,16 +3890,16 @@
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.2">
@@ -3910,112 +3907,112 @@
         <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="J25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="U25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE25" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD25" s="2" t="s">
+      <c r="AF25" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AE25" s="2" t="s">
+      <c r="AG25" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AF25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AG25" s="2" t="s">
+      <c r="AH25" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AH25" s="2" t="s">
+      <c r="AI25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AI25" s="2" t="s">
+      <c r="AJ25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AJ25" s="2" t="s">
+      <c r="AK25" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="AK25" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="AL25" s="2"/>
       <c r="AM25" s="2"/>
@@ -4073,16 +4070,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -4090,55 +4087,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -4150,16 +4147,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -4167,49 +4164,49 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -4256,16 +4253,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -4273,28 +4270,28 @@
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.2">
@@ -4309,16 +4306,16 @@
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.2">
@@ -4326,13 +4323,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -4347,16 +4344,16 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.2">
@@ -4364,25 +4361,25 @@
         <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.2">
@@ -4399,16 +4396,16 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.2">
@@ -4416,25 +4413,25 @@
         <v>17</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="H30" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>82</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -4489,16 +4486,16 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -4506,58 +4503,58 @@
         <v>17</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J36" s="1" t="s">
+      <c r="M36" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P36" s="1" t="s">
+      <c r="R36" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="S36" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -4572,16 +4569,16 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -4589,16 +4586,16 @@
         <v>17</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -4616,16 +4613,16 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -4633,22 +4630,22 @@
         <v>17</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -4679,16 +4676,16 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
@@ -4696,31 +4693,31 @@
         <v>17</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="I53" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="J53" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
@@ -4730,16 +4727,16 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
@@ -4747,22 +4744,22 @@
         <v>17</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -4778,16 +4775,16 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -4795,22 +4792,22 @@
         <v>17</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -4820,16 +4817,16 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -4837,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -4858,16 +4855,16 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -4875,34 +4872,34 @@
         <v>17</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4912,16 +4909,16 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -4929,22 +4926,22 @@
         <v>17</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F74" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -4959,16 +4956,16 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
@@ -4976,25 +4973,25 @@
         <v>17</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="G79" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -5032,16 +5029,16 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -5049,55 +5046,55 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="R2" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
